--- a/output/graficos_regionales_piramide/plot_regional_piramide_2020_los_lagos.xlsx
+++ b/output/graficos_regionales_piramide/plot_regional_piramide_2020_los_lagos.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-30 15:41</t>
+    <t xml:space="preserve">2026-10-05 21:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
